--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008545626218323586</v>
       </c>
       <c r="C2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>51101083</v>
+        <v>3724409</v>
       </c>
       <c r="L2" t="n">
-        <v>27102819</v>
+        <v>1704582</v>
       </c>
       <c r="M2" t="n">
-        <v>6047007</v>
+        <v>320106</v>
       </c>
       <c r="N2" t="n">
-        <v>195860</v>
+        <v>9555</v>
       </c>
       <c r="O2" t="n">
-        <v>3579237</v>
+        <v>166732</v>
       </c>
       <c r="P2" t="n">
-        <v>1396863</v>
+        <v>66757</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999958276748657</v>
+        <v>0.9999990463256836</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8274449110031128</v>
+        <v>0.7195658683776855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6748179793357849</v>
+        <v>0.5079741477966309</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5903534293174744</v>
+        <v>0.3785123527050018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1553190797567368</v>
+        <v>0.05079042911529541</v>
       </c>
       <c r="V2" t="n">
-        <v>0.644432544708252</v>
+        <v>0.4334776997566223</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7525617480278015</v>
+        <v>0.5581828951835632</v>
       </c>
       <c r="X2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>76156560</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="AG2" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AH2" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AI2" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558068513870239</v>
+        <v>0.9542856216430664</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117310047149658</v>
+        <v>0.9129269123077393</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579899072647095</v>
+        <v>0.857567310333252</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6614375710487366</v>
+        <v>0.6599931120872498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019421935081482</v>
+        <v>0.9016656875610352</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002047782815014169</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>51101083</v>
+        <v>3724409</v>
       </c>
       <c r="E3" t="n">
-        <v>8901223</v>
+        <v>1158979</v>
       </c>
       <c r="F3" t="n">
-        <v>340834</v>
+        <v>73014</v>
       </c>
       <c r="G3" t="n">
-        <v>29802</v>
+        <v>8894</v>
       </c>
       <c r="H3" t="n">
-        <v>31066</v>
+        <v>6562</v>
       </c>
       <c r="I3" t="n">
-        <v>3171</v>
+        <v>774</v>
       </c>
       <c r="J3" t="n">
-        <v>120835121</v>
+        <v>10069614</v>
       </c>
       <c r="K3" t="n">
-        <v>125928186</v>
+        <v>9991864</v>
       </c>
       <c r="L3" t="n">
-        <v>144284985</v>
+        <v>11411482</v>
       </c>
       <c r="M3" t="n">
-        <v>181539996</v>
+        <v>14944286</v>
       </c>
       <c r="N3" t="n">
-        <v>194851152</v>
+        <v>16147193</v>
       </c>
       <c r="O3" t="n">
-        <v>188889865</v>
+        <v>15684972</v>
       </c>
       <c r="P3" t="n">
-        <v>194210124</v>
+        <v>16169110</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8459434509277344</v>
+        <v>0.7489811182022095</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6836088299751282</v>
+        <v>0.5083065032958984</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5372260212898254</v>
+        <v>0.3383337259292603</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1820783168077469</v>
+        <v>0.1058889999985695</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5841476917266846</v>
+        <v>0.3249363601207733</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6014233827590942</v>
+        <v>0.3440195918083191</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57839739</v>
+        <v>4760658</v>
       </c>
       <c r="Z3" t="n">
-        <v>2382014</v>
+        <v>196517</v>
       </c>
       <c r="AA3" t="n">
-        <v>102565</v>
+        <v>8569</v>
       </c>
       <c r="AB3" t="n">
-        <v>82163</v>
+        <v>6849</v>
       </c>
       <c r="AC3" t="n">
-        <v>370</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120835440</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>133910484</v>
+        <v>11215310</v>
       </c>
       <c r="AG3" t="n">
-        <v>153853413</v>
+        <v>12771731</v>
       </c>
       <c r="AH3" t="n">
-        <v>184139493</v>
+        <v>15335364</v>
       </c>
       <c r="AI3" t="n">
-        <v>195552500</v>
+        <v>16295127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>190264326</v>
+        <v>15852474</v>
       </c>
       <c r="AK3" t="n">
-        <v>194510227</v>
+        <v>16208628</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.957497239112854</v>
+        <v>0.9573714733123779</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097340106964111</v>
+        <v>0.9092389345169067</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8569492101669312</v>
+        <v>0.8559883832931519</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.660748302936554</v>
+        <v>0.6590496301651001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9012896418571472</v>
+        <v>0.9007097482681274</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03221459809678776</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>9796307</v>
+        <v>1290176</v>
       </c>
       <c r="E4" t="n">
-        <v>27102819</v>
+        <v>1704582</v>
       </c>
       <c r="F4" t="n">
-        <v>2262312</v>
+        <v>271550</v>
       </c>
       <c r="G4" t="n">
-        <v>147543</v>
+        <v>37546</v>
       </c>
       <c r="H4" t="n">
-        <v>298952</v>
+        <v>43045</v>
       </c>
       <c r="I4" t="n">
-        <v>38742</v>
+        <v>6554</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>10656603</v>
+        <v>1451502</v>
       </c>
       <c r="L4" t="n">
-        <v>13060336</v>
+        <v>1651065</v>
       </c>
       <c r="M4" t="n">
-        <v>4196021</v>
+        <v>525589</v>
       </c>
       <c r="N4" t="n">
-        <v>1065157</v>
+        <v>178571</v>
       </c>
       <c r="O4" t="n">
-        <v>1974854</v>
+        <v>217906</v>
       </c>
       <c r="P4" t="n">
-        <v>459281</v>
+        <v>52840</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999979138374329</v>
+        <v>0.9999995231628418</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8365919589996338</v>
+        <v>0.7339789271354675</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6791849732398987</v>
+        <v>0.5081403255462646</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5625381469726562</v>
+        <v>0.3572970628738403</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1676375418901443</v>
+        <v>0.06865161657333374</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6128110289573669</v>
+        <v>0.3714400231838226</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6685571670532227</v>
+        <v>0.42568239569664</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2497781</v>
+        <v>213160</v>
       </c>
       <c r="Z4" t="n">
-        <v>36067932</v>
+        <v>3049090</v>
       </c>
       <c r="AA4" t="n">
-        <v>999552</v>
+        <v>84162</v>
       </c>
       <c r="AB4" t="n">
-        <v>66772</v>
+        <v>5695</v>
       </c>
       <c r="AC4" t="n">
-        <v>13821</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2674305</v>
+        <v>228056</v>
       </c>
       <c r="AG4" t="n">
-        <v>3491908</v>
+        <v>290816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1596524</v>
+        <v>134511</v>
       </c>
       <c r="AI4" t="n">
-        <v>363809</v>
+        <v>30637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600393</v>
+        <v>50404</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566512703895569</v>
+        <v>0.9558260440826416</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107314348220825</v>
+        <v>0.9110792279243469</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574692010879517</v>
+        <v>0.8567771315574646</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6610927581787109</v>
+        <v>0.6595210433006287</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016157984733582</v>
+        <v>0.9011874794960022</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>619161</v>
+        <v>118818</v>
       </c>
       <c r="E5" t="n">
-        <v>3343852</v>
+        <v>357022</v>
       </c>
       <c r="F5" t="n">
-        <v>6047007</v>
+        <v>320106</v>
       </c>
       <c r="G5" t="n">
-        <v>317568</v>
+        <v>49918</v>
       </c>
       <c r="H5" t="n">
-        <v>819754</v>
+        <v>84877</v>
       </c>
       <c r="I5" t="n">
-        <v>108622</v>
+        <v>15384</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9306128</v>
+        <v>1248225</v>
       </c>
       <c r="L5" t="n">
-        <v>12543860</v>
+        <v>1648871</v>
       </c>
       <c r="M5" t="n">
-        <v>5208976</v>
+        <v>626019</v>
       </c>
       <c r="N5" t="n">
-        <v>879831</v>
+        <v>80681</v>
       </c>
       <c r="O5" t="n">
-        <v>2548044</v>
+        <v>346390</v>
       </c>
       <c r="P5" t="n">
-        <v>925732</v>
+        <v>127293</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999983906745911</v>
+        <v>0.9999996423721313</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8986622095108032</v>
+        <v>0.8355429172515869</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8700242042541504</v>
+        <v>0.7989805340766907</v>
       </c>
       <c r="T5" t="n">
-        <v>0.952256977558136</v>
+        <v>0.9298484325408936</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9901265501976013</v>
+        <v>0.9842073321342468</v>
       </c>
       <c r="V5" t="n">
-        <v>0.97704017162323</v>
+        <v>0.9656252264976501</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9929692149162292</v>
+        <v>0.9890269637107849</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>97322</v>
+        <v>8204</v>
       </c>
       <c r="Z5" t="n">
-        <v>1034594</v>
+        <v>87997</v>
       </c>
       <c r="AA5" t="n">
-        <v>9645806</v>
+        <v>809872</v>
       </c>
       <c r="AB5" t="n">
-        <v>119997</v>
+        <v>10066</v>
       </c>
       <c r="AC5" t="n">
-        <v>350660</v>
+        <v>29345</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2567472</v>
+        <v>211976</v>
       </c>
       <c r="AG5" t="n">
-        <v>3578747</v>
+        <v>304363</v>
       </c>
       <c r="AH5" t="n">
-        <v>1610177</v>
+        <v>136253</v>
       </c>
       <c r="AI5" t="n">
-        <v>364930</v>
+        <v>30766</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604826</v>
+        <v>50948</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9733909368515015</v>
+        <v>0.97319495677948</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641069173812866</v>
+        <v>0.9637439846992493</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837216734886169</v>
+        <v>0.9835060834884644</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963006377220154</v>
+        <v>0.9962595701217651</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.99388188123703</v>
+        <v>0.9938260316848755</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983799457550049</v>
+        <v>0.9983697533607483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>173259</v>
+        <v>20740</v>
       </c>
       <c r="E6" t="n">
-        <v>268646</v>
+        <v>27131</v>
       </c>
       <c r="F6" t="n">
-        <v>313134</v>
+        <v>22710</v>
       </c>
       <c r="G6" t="n">
-        <v>195860</v>
+        <v>9555</v>
       </c>
       <c r="H6" t="n">
-        <v>111090</v>
+        <v>8606</v>
       </c>
       <c r="I6" t="n">
-        <v>13634</v>
+        <v>1490</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78611</v>
+        <v>6656</v>
       </c>
       <c r="Z6" t="n">
-        <v>64601</v>
+        <v>5410</v>
       </c>
       <c r="AA6" t="n">
-        <v>131879</v>
+        <v>11168</v>
       </c>
       <c r="AB6" t="n">
-        <v>710761</v>
+        <v>59470</v>
       </c>
       <c r="AC6" t="n">
-        <v>84061</v>
+        <v>7046</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>63558</v>
+        <v>19782</v>
       </c>
       <c r="E7" t="n">
-        <v>494539</v>
+        <v>95242</v>
       </c>
       <c r="F7" t="n">
-        <v>1171152</v>
+        <v>134812</v>
       </c>
       <c r="G7" t="n">
-        <v>523672</v>
+        <v>67916</v>
       </c>
       <c r="H7" t="n">
-        <v>3579237</v>
+        <v>166732</v>
       </c>
       <c r="I7" t="n">
-        <v>295112</v>
+        <v>28638</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9726</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358547</v>
+        <v>30278</v>
       </c>
       <c r="AB7" t="n">
-        <v>91683</v>
+        <v>7760</v>
       </c>
       <c r="AC7" t="n">
-        <v>5522455</v>
+        <v>462174</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4318</v>
+        <v>1986</v>
       </c>
       <c r="E8" t="n">
-        <v>52076</v>
+        <v>12691</v>
       </c>
       <c r="F8" t="n">
-        <v>108589</v>
+        <v>23503</v>
       </c>
       <c r="G8" t="n">
-        <v>46572</v>
+        <v>14297</v>
       </c>
       <c r="H8" t="n">
-        <v>713992</v>
+        <v>74816</v>
       </c>
       <c r="I8" t="n">
-        <v>1396863</v>
+        <v>66757</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
